--- a/healthcare_forms/025_health_initiative_referral_form--healthcare_forms.xlsx
+++ b/healthcare_forms/025_health_initiative_referral_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'health_initiative',_'label':_'health_initiative'}</t>
+          <t>health_initiative</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'health_initiative', 'label': 'Health Initiative'}</t>
+          <t>Health Initiative</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'health_initiative_1',_'label':_'health_initiative_1'}</t>
+          <t>health_initiative_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'health_initiative_1', 'label': 'Health Initiative 1'}</t>
+          <t>Health Initiative 1</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'health_initiative_2',_'label':_'health_initiative_2'}</t>
+          <t>health_initiative_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'health_initiative_2', 'label': 'Health Initiative 2'}</t>
+          <t>Health Initiative 2</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'health_initiative_3',_'label':_'health_initiative_3'}</t>
+          <t>health_initiative_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'health_initiative_3', 'label': 'Health Initiative 3'}</t>
+          <t>Health Initiative 3</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'phone',_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'phone', 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'email',_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'email', 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'mail',_'label':_'mail'}</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'mail', 'label': 'Mail'}</t>
+          <t>Mail</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'daily',_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'daily', 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'weekly',_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'weekly', 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'monthly',_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'monthly', 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'phone',_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'phone', 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'email',_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'email', 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'mail',_'label':_'mail'}</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'mail', 'label': 'Mail'}</t>
+          <t>Mail</t>
         </is>
       </c>
     </row>
